--- a/artfynd/A 8063-2024 artfynd.xlsx
+++ b/artfynd/A 8063-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125629652</v>
+        <v>125629711</v>
       </c>
       <c r="B2" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471661</v>
+        <v>471642</v>
       </c>
       <c r="R2" t="n">
-        <v>6551993</v>
+        <v>6552015</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125629711</v>
+        <v>125629652</v>
       </c>
       <c r="B3" t="n">
-        <v>106734</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,16 +788,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>245</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471642</v>
+        <v>471661</v>
       </c>
       <c r="R3" t="n">
-        <v>6552015</v>
+        <v>6551993</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 8063-2024 artfynd.xlsx
+++ b/artfynd/A 8063-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125629711</v>
       </c>
       <c r="B2" t="n">
-        <v>106789</v>
+        <v>106796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125629652</v>
       </c>
       <c r="B3" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8063-2024 artfynd.xlsx
+++ b/artfynd/A 8063-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125629711</v>
       </c>
       <c r="B2" t="n">
-        <v>106796</v>
+        <v>106799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125629652</v>
       </c>
       <c r="B3" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8063-2024 artfynd.xlsx
+++ b/artfynd/A 8063-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125629711</v>
       </c>
       <c r="B2" t="n">
-        <v>106799</v>
+        <v>106803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125629652</v>
       </c>
       <c r="B3" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8063-2024 artfynd.xlsx
+++ b/artfynd/A 8063-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125629711</v>
       </c>
       <c r="B2" t="n">
-        <v>106803</v>
+        <v>106804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125629652</v>
       </c>
       <c r="B3" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8063-2024 artfynd.xlsx
+++ b/artfynd/A 8063-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125629711</v>
       </c>
       <c r="B2" t="n">
-        <v>106804</v>
+        <v>106806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125629652</v>
       </c>
       <c r="B3" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8063-2024 artfynd.xlsx
+++ b/artfynd/A 8063-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125629711</v>
       </c>
       <c r="B2" t="n">
-        <v>106806</v>
+        <v>106808</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125629652</v>
       </c>
       <c r="B3" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8063-2024 artfynd.xlsx
+++ b/artfynd/A 8063-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125629711</v>
       </c>
       <c r="B2" t="n">
-        <v>106808</v>
+        <v>106812</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125629652</v>
       </c>
       <c r="B3" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8063-2024 artfynd.xlsx
+++ b/artfynd/A 8063-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125629711</v>
       </c>
       <c r="B2" t="n">
-        <v>106812</v>
+        <v>106825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125629652</v>
       </c>
       <c r="B3" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8063-2024 artfynd.xlsx
+++ b/artfynd/A 8063-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125629711</v>
       </c>
       <c r="B2" t="n">
-        <v>106837</v>
+        <v>106912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8063-2024 artfynd.xlsx
+++ b/artfynd/A 8063-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125629711</v>
       </c>
       <c r="B2" t="n">
-        <v>106912</v>
+        <v>106918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8063-2024 artfynd.xlsx
+++ b/artfynd/A 8063-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125629711</v>
       </c>
       <c r="B2" t="n">
-        <v>106918</v>
+        <v>106919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8063-2024 artfynd.xlsx
+++ b/artfynd/A 8063-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125629711</v>
       </c>
       <c r="B2" t="n">
-        <v>106919</v>
+        <v>106912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8063-2024 artfynd.xlsx
+++ b/artfynd/A 8063-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>125629711</v>
       </c>
       <c r="B2" t="n">
-        <v>106919</v>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>125629652</v>
       </c>
       <c r="B3" t="n">
-        <v>109173</v>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,6 +898,211 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125629581</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106061</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221101</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Impatiens noli-tangere</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Larsbo, V om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>471716</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6552000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Fuktig till våt barjord vid dike. Gammal granplanterad åkermark.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125629710</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102563</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Larsbo, V om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>471642</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6552015</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägkant/dike/slänt</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8063-2024 artfynd.xlsx
+++ b/artfynd/A 8063-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125629711</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125629652</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125629581</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,8 +1123,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125629710</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>